--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4115" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4115" uniqueCount="577">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -672,7 +672,7 @@
 </t>
   </si>
   <si>
-    <t>Specific type of encounter</t>
+    <t>Type de prise en charge</t>
   </si>
   <si>
     <t>Specific type of encounter (e.g. e-mail consultation, surgical day-care, skilled nursing, rehabilitation).</t>
@@ -934,6 +934,9 @@
     <t>Encounter.participant:Responsable.type</t>
   </si>
   <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
     <t>Encounter.participant:Responsable.type.id</t>
   </si>
   <si>
@@ -1168,6 +1171,9 @@
 </t>
   </si>
   <si>
+    <t>Entité responsable de la prise en charge</t>
+  </si>
+  <si>
     <t>Encounter.participant:Personne-Impliquee</t>
   </si>
   <si>
@@ -1208,6 +1214,9 @@
   </si>
   <si>
     <t>Encounter.participant:Personne-Impliquee.individual</t>
+  </si>
+  <si>
+    <t>Professionnel impliqué</t>
   </si>
   <si>
     <t>Encounter.appointment</t>
@@ -1232,7 +1241,7 @@
     <t>Encounter.period</t>
   </si>
   <si>
-    <t>The start and end time of the encounter</t>
+    <t>Date de début et de fin de la prise en charge</t>
   </si>
   <si>
     <t>The start and end time of the encounter.</t>
@@ -1596,7 +1605,7 @@
     <t>Encounter.hospitalization.dischargeDisposition</t>
   </si>
   <si>
-    <t>Category or kind of location after discharge</t>
+    <t>Type sortie</t>
   </si>
   <si>
     <t>Category or kind of location after discharge.</t>
@@ -1653,7 +1662,7 @@
     <t>Encounter.location</t>
   </si>
   <si>
-    <t>List of locations where the patient has been</t>
+    <t>Lieu de la prise en charge</t>
   </si>
   <si>
     <t>List of locations where  the patient has been during this encounter.</t>
@@ -6926,7 +6935,7 @@
         <v>210</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="M43" t="s" s="2">
         <v>270</v>
@@ -7011,10 +7020,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7123,10 +7132,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7196,10 +7205,10 @@
         <v>79</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>79</v>
@@ -7237,10 +7246,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7266,16 +7275,16 @@
         <v>188</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7324,7 +7333,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7342,21 +7351,21 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7465,10 +7474,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7538,10 +7547,10 @@
         <v>79</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>79</v>
@@ -7579,10 +7588,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7608,16 +7617,16 @@
         <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7627,7 +7636,7 @@
         <v>79</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>79</v>
@@ -7666,7 +7675,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7684,21 +7693,21 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7724,13 +7733,13 @@
         <v>170</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7780,7 +7789,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7798,21 +7807,21 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7838,14 +7847,14 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -7855,7 +7864,7 @@
         <v>79</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>79</v>
@@ -7894,7 +7903,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7912,21 +7921,21 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7952,14 +7961,14 @@
         <v>170</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7969,7 +7978,7 @@
         <v>79</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>79</v>
@@ -8008,7 +8017,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -8026,21 +8035,21 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8063,19 +8072,19 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8124,7 +8133,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8142,21 +8151,21 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8182,16 +8191,16 @@
         <v>170</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8240,7 +8249,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8258,18 +8267,18 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>276</v>
@@ -8381,7 +8390,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>281</v>
@@ -8407,10 +8416,10 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>283</v>
+        <v>374</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>284</v>
@@ -8493,13 +8502,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>257</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>79</v>
@@ -8524,7 +8533,7 @@
         <v>164</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>259</v>
@@ -8607,7 +8616,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>265</v>
@@ -8719,7 +8728,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>266</v>
@@ -8833,7 +8842,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>267</v>
@@ -8949,7 +8958,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>268</v>
@@ -8978,7 +8987,7 @@
         <v>210</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="M61" t="s" s="2">
         <v>270</v>
@@ -9063,10 +9072,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9175,10 +9184,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9248,10 +9257,10 @@
         <v>79</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>79</v>
@@ -9289,10 +9298,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9318,16 +9327,16 @@
         <v>188</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -9356,7 +9365,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9374,7 +9383,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9392,21 +9401,21 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9432,16 +9441,16 @@
         <v>170</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9490,7 +9499,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9508,18 +9517,18 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>276</v>
@@ -9631,7 +9640,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>281</v>
@@ -9657,10 +9666,10 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>283</v>
+        <v>389</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>284</v>
@@ -9743,10 +9752,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9769,13 +9778,13 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9826,7 +9835,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9844,21 +9853,21 @@
         <v>255</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9884,13 +9893,13 @@
         <v>184</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9940,7 +9949,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9955,24 +9964,24 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9995,16 +10004,16 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10054,7 +10063,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -10069,28 +10078,28 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10112,13 +10121,13 @@
         <v>210</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10147,10 +10156,10 @@
         <v>111</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -10168,7 +10177,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10183,28 +10192,28 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10223,16 +10232,16 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10282,7 +10291,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10297,24 +10306,24 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10340,10 +10349,10 @@
         <v>164</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10394,7 +10403,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10412,7 +10421,7 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
@@ -10423,10 +10432,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10535,10 +10544,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10649,10 +10658,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10765,14 +10774,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10791,16 +10800,16 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10850,7 +10859,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>87</v>
@@ -10865,24 +10874,24 @@
         <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10908,10 +10917,10 @@
         <v>210</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10941,28 +10950,28 @@
         <v>111</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10991,10 +11000,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11017,13 +11026,13 @@
         <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11074,7 +11083,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -11092,7 +11101,7 @@
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>79</v>
@@ -11103,10 +11112,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11129,16 +11138,16 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11188,7 +11197,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11206,7 +11215,7 @@
         <v>79</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>79</v>
@@ -11217,10 +11226,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11246,13 +11255,13 @@
         <v>164</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11302,7 +11311,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11320,7 +11329,7 @@
         <v>79</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>79</v>
@@ -11331,10 +11340,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11443,10 +11452,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11557,10 +11566,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11673,10 +11682,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11702,10 +11711,10 @@
         <v>145</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11756,7 +11765,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -11780,15 +11789,15 @@
         <v>79</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11811,13 +11820,13 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11868,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -11886,7 +11895,7 @@
         <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>79</v>
@@ -11897,10 +11906,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11926,10 +11935,10 @@
         <v>210</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11959,28 +11968,28 @@
         <v>111</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -11998,21 +12007,21 @@
         <v>79</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12038,10 +12047,10 @@
         <v>210</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12071,28 +12080,28 @@
         <v>214</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -12116,15 +12125,15 @@
         <v>79</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12150,16 +12159,16 @@
         <v>210</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12187,10 +12196,10 @@
         <v>214</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>79</v>
@@ -12208,7 +12217,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12226,21 +12235,21 @@
         <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12266,10 +12275,10 @@
         <v>210</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12299,28 +12308,28 @@
         <v>111</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -12338,21 +12347,21 @@
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12378,10 +12387,10 @@
         <v>210</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12411,28 +12420,28 @@
         <v>111</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -12450,21 +12459,21 @@
         <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12487,13 +12496,13 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12544,7 +12553,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -12562,21 +12571,21 @@
         <v>79</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12602,10 +12611,10 @@
         <v>210</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12635,28 +12644,28 @@
         <v>214</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -12674,21 +12683,21 @@
         <v>79</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12797,10 +12806,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12870,10 +12879,10 @@
         <v>79</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>79</v>
@@ -12911,10 +12920,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12940,16 +12949,16 @@
         <v>188</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>79</v>
@@ -12998,7 +13007,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -13016,21 +13025,21 @@
         <v>79</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13139,10 +13148,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13212,10 +13221,10 @@
         <v>79</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>79</v>
@@ -13253,10 +13262,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13282,16 +13291,16 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>79</v>
@@ -13301,7 +13310,7 @@
         <v>79</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>79</v>
@@ -13340,7 +13349,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -13358,21 +13367,21 @@
         <v>79</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13398,13 +13407,13 @@
         <v>170</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13454,7 +13463,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -13472,21 +13481,21 @@
         <v>79</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13512,14 +13521,14 @@
         <v>107</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>79</v>
@@ -13568,7 +13577,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -13586,21 +13595,21 @@
         <v>79</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13626,14 +13635,14 @@
         <v>170</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>79</v>
@@ -13682,7 +13691,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13700,21 +13709,21 @@
         <v>79</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13737,19 +13746,19 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>79</v>
@@ -13798,7 +13807,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13816,21 +13825,21 @@
         <v>79</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13856,16 +13865,16 @@
         <v>170</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>79</v>
@@ -13914,7 +13923,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -13932,21 +13941,21 @@
         <v>79</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13972,13 +13981,13 @@
         <v>164</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14028,7 +14037,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
@@ -14046,7 +14055,7 @@
         <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>79</v>
@@ -14057,10 +14066,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14169,10 +14178,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14283,10 +14292,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14399,10 +14408,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14425,13 +14434,13 @@
         <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14482,7 +14491,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>87</v>
@@ -14497,24 +14506,24 @@
         <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>286</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14540,13 +14549,13 @@
         <v>107</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14575,10 +14584,10 @@
         <v>156</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>79</v>
@@ -14596,7 +14605,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -14614,7 +14623,7 @@
         <v>79</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>79</v>
@@ -14625,10 +14634,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14654,13 +14663,13 @@
         <v>210</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14689,10 +14698,10 @@
         <v>214</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>79</v>
@@ -14710,7 +14719,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -14739,10 +14748,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14768,10 +14777,10 @@
         <v>184</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14822,7 +14831,7 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -14851,10 +14860,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14877,13 +14886,13 @@
         <v>79</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14934,7 +14943,7 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
@@ -14952,21 +14961,21 @@
         <v>285</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14989,16 +14998,16 @@
         <v>79</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15048,7 +15057,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -15063,10 +15072,10 @@
         <v>99</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>79</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2434,17 +2434,17 @@
   <dimension ref="A1:AN143"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="63.30078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="63.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.87109375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="54.26953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="54.26953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="20.46484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="125.98046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="108.0078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2453,26 +2453,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="114.9609375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.67578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="98.55859375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.16015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="191.1328125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="163.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
